--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">226474</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F4">
-        <v>372</v>
+        <v>284</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831848</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F5">
-        <v>681</v>
+        <v>524</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,30 +281,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163597</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F6">
-        <v>899</v>
+        <v>704</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027302</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-27</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -331,30 +331,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">226935, 226960, 226936, 226937, 226938, 226939, 226940, 226941, 226942, 226943, 226944, 226945, 226947, 226948, 226949, 226950, 226951, 226952, 226953, 226954, 226955, 226956, 226958, 226959, 226961, 226963, 226964, 226965, 226966, 226967, 226968, 226946, 226957</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F7">
-        <v>4989</v>
+        <v>704</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">310011650</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-02</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -381,35 +381,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115661</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F8">
-        <v>342</v>
+        <v>704</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299608</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -431,35 +431,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115669</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F9">
-        <v>732</v>
+        <v>524</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317842</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -481,35 +481,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">226530</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F10">
-        <v>13498</v>
+        <v>2564</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350678</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-09</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -531,35 +531,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">226935, 226960, 226936, 226937, 226938, 226939, 226940, 226941, 226942, 226943, 226944, 226945, 226947, 226948, 226949, 226950, 226951, 226952, 226953, 226954, 226955, 226956, 226958, 226959, 226961, 226963, 226964, 226965, 226966, 226967, 226968, 226946, 226957</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>418</v>
+        <v>4989</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350679</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-09</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -594,22 +594,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366317</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-22</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -631,35 +631,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">227000, 227001</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>524</v>
+        <v>3449</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366950</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F14">
-        <v>704</v>
+        <v>372</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366950</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -731,25 +731,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2115661</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F15">
-        <v>704</v>
+        <v>342</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366950</t>
+          <t xml:space="preserve">311299608</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2115669</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366950</t>
+          <t xml:space="preserve">311317842</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,25 +831,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>524</v>
+        <v>13498</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366950</t>
+          <t xml:space="preserve">311350678</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">226530</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,16 +890,16 @@
         </is>
       </c>
       <c r="F18">
-        <v>2564</v>
+        <v>418</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366938</t>
+          <t xml:space="preserve">311350679</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-26</t>
+          <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1036,20 +1036,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>1830</v>
+        <v>899</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726435</t>
+          <t xml:space="preserve">311726167</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-02</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831839</t>
+          <t xml:space="preserve">2163597</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F22">
-        <v>1713</v>
+        <v>1830</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773114</t>
+          <t xml:space="preserve">311726435</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-12</t>
+          <t xml:space="preserve">2033-12-02</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840080</t>
+          <t xml:space="preserve">311840069</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840071</t>
+          <t xml:space="preserve">311840069</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">227000, 227001</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F29">
-        <v>3449</v>
+        <v>2478</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840059</t>
+          <t xml:space="preserve">311840061</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">2113481</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F30">
-        <v>2478</v>
+        <v>2184</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840061</t>
+          <t xml:space="preserve">311840942</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-23</t>
+          <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1531,25 +1531,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263211</t>
+          <t xml:space="preserve">2114982</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F31">
-        <v>718</v>
+        <v>445</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840067</t>
+          <t xml:space="preserve">311841018</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-23</t>
+          <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113481</t>
+          <t xml:space="preserve">2115125</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,11 +1590,11 @@
         </is>
       </c>
       <c r="F32">
-        <v>2184</v>
+        <v>3395</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840942</t>
+          <t xml:space="preserve">311840944</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114982</t>
+          <t xml:space="preserve">7332315</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1640,11 +1640,11 @@
         </is>
       </c>
       <c r="F33">
-        <v>445</v>
+        <v>573</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841018</t>
+          <t xml:space="preserve">311841026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1681,20 +1681,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115125</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>3395</v>
+        <v>758</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840944</t>
+          <t xml:space="preserve">311841028</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7332315</t>
+          <t xml:space="preserve">2114362</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="F35">
-        <v>573</v>
+        <v>1238</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841026</t>
+          <t xml:space="preserve">311843211</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-26</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">2115661</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F36">
-        <v>758</v>
+        <v>822</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841028</t>
+          <t xml:space="preserve">311843204</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-26</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114362</t>
+          <t xml:space="preserve">2116268</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,11 +1840,11 @@
         </is>
       </c>
       <c r="F37">
-        <v>1238</v>
+        <v>771</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843211</t>
+          <t xml:space="preserve">311843205</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115661</t>
+          <t xml:space="preserve">2162900</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="F38">
-        <v>822</v>
+        <v>498</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843204</t>
+          <t xml:space="preserve">311843217</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,20 +1931,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116268</t>
+          <t xml:space="preserve">2162900</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39">
-        <v>771</v>
+        <v>444</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843205</t>
+          <t xml:space="preserve">311843217</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,20 +1981,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162668</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>639</v>
+        <v>718</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843209</t>
+          <t xml:space="preserve">311843214</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162900</t>
+          <t xml:space="preserve">8831859</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="F41">
-        <v>498</v>
+        <v>682</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843217</t>
+          <t xml:space="preserve">311843203</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162900</t>
+          <t xml:space="preserve">8831895</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>444</v>
+        <v>566</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843217</t>
+          <t xml:space="preserve">311846822</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-07-31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">100035364</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,16 +2140,16 @@
         </is>
       </c>
       <c r="F43">
-        <v>718</v>
+        <v>2396</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843214</t>
+          <t xml:space="preserve">311847170</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-08-04</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831859</t>
+          <t xml:space="preserve">8831861</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2190,16 +2190,16 @@
         </is>
       </c>
       <c r="F44">
-        <v>682</v>
+        <v>2783</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843203</t>
+          <t xml:space="preserve">311852544</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831895</t>
+          <t xml:space="preserve">2115105</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F45">
-        <v>566</v>
+        <v>931</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846822</t>
+          <t xml:space="preserve">311855424</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-31</t>
+          <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035364</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F46">
-        <v>2396</v>
+        <v>675</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847170</t>
+          <t xml:space="preserve">311855487</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-04</t>
+          <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831861</t>
+          <t xml:space="preserve">100041701</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,16 +2340,16 @@
         </is>
       </c>
       <c r="F47">
-        <v>2783</v>
+        <v>3088</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852544</t>
+          <t xml:space="preserve">311857077</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115105</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>931</v>
+        <v>13180</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855424</t>
+          <t xml:space="preserve">311857073</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-12</t>
+          <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F49">
-        <v>675</v>
+        <v>1707</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855487</t>
+          <t xml:space="preserve">311857072</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-12</t>
+          <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164045</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F50">
-        <v>680</v>
+        <v>616</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855479</t>
+          <t xml:space="preserve">311857071</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-12</t>
+          <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,20 +2531,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100041701</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F51">
-        <v>3088</v>
+        <v>1133</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857077</t>
+          <t xml:space="preserve">311857078</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2581,20 +2581,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8209831</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F52">
-        <v>13180</v>
+        <v>673</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857073</t>
+          <t xml:space="preserve">311857070</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2631,20 +2631,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>1707</v>
+        <v>11175</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857072</t>
+          <t xml:space="preserve">311857074</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2681,20 +2681,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F54">
-        <v>616</v>
+        <v>545</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857071</t>
+          <t xml:space="preserve">311857075</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2731,20 +2731,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F55">
-        <v>1133</v>
+        <v>2856</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857078</t>
+          <t xml:space="preserve">311857076</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8209831</t>
+          <t xml:space="preserve">2114359</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>673</v>
+        <v>254</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857070</t>
+          <t xml:space="preserve">311858017</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-20</t>
+          <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">10081434</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>11175</v>
+        <v>4875</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857074</t>
+          <t xml:space="preserve">311860092</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-20</t>
+          <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">2113993</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F58">
-        <v>545</v>
+        <v>713</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857075</t>
+          <t xml:space="preserve">311860093</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-20</t>
+          <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">2115649</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>2856</v>
+        <v>6380</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857076</t>
+          <t xml:space="preserve">311860572</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-20</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114359</t>
+          <t xml:space="preserve">2115649</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F60">
-        <v>254</v>
+        <v>4013</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858017</t>
+          <t xml:space="preserve">311860572</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-25</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081434</t>
+          <t xml:space="preserve">1302613</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F61">
-        <v>4875</v>
+        <v>588</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860092</t>
+          <t xml:space="preserve">311863004</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-06</t>
+          <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113993</t>
+          <t xml:space="preserve">2112485</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>713</v>
+        <v>1243</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860093</t>
+          <t xml:space="preserve">311863027</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-06</t>
+          <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115649</t>
+          <t xml:space="preserve">2113993</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="F63">
-        <v>6380</v>
+        <v>10309</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860572</t>
+          <t xml:space="preserve">311867275</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115649</t>
+          <t xml:space="preserve">2162639</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F64">
-        <v>4013</v>
+        <v>534</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860572</t>
+          <t xml:space="preserve">311863019</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,20 +3231,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302613</t>
+          <t xml:space="preserve">8209831</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>588</v>
+        <v>1006</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863006</t>
+          <t xml:space="preserve">311863018</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112485</t>
+          <t xml:space="preserve">8831824</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3290,11 +3290,11 @@
         </is>
       </c>
       <c r="F66">
-        <v>1243</v>
+        <v>257</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863027</t>
+          <t xml:space="preserve">311862953</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113993</t>
+          <t xml:space="preserve">2163948</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>10309</v>
+        <v>543</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867275</t>
+          <t xml:space="preserve">311864426</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-10-27</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162639</t>
+          <t xml:space="preserve">2114474</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F68">
-        <v>534</v>
+        <v>2016</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863022</t>
+          <t xml:space="preserve">311867157</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-11-09</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164045</t>
+          <t xml:space="preserve">2162668</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F69">
-        <v>689</v>
+        <v>639</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863008</t>
+          <t xml:space="preserve">311867872</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8209831</t>
+          <t xml:space="preserve">2164045</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F70">
-        <v>1006</v>
+        <v>680</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863018</t>
+          <t xml:space="preserve">311867867</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831824</t>
+          <t xml:space="preserve">2164045</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F71">
-        <v>257</v>
+        <v>689</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862953</t>
+          <t xml:space="preserve">311867867</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831848</t>
+          <t xml:space="preserve">100095721</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>528</v>
+        <v>1770</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867289</t>
+          <t xml:space="preserve">311868121</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831848</t>
+          <t xml:space="preserve">2112535</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>7706</v>
+        <v>359</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863480</t>
+          <t xml:space="preserve">311868258</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-22</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163948</t>
+          <t xml:space="preserve">8831831</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>543</v>
+        <v>10887</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864426</t>
+          <t xml:space="preserve">311868487</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-27</t>
+          <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114474</t>
+          <t xml:space="preserve">2114042</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,16 +3740,16 @@
         </is>
       </c>
       <c r="F75">
-        <v>2016</v>
+        <v>1096</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867157</t>
+          <t xml:space="preserve">311869557</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-09</t>
+          <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100095721</t>
+          <t xml:space="preserve">2114432</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>1770</v>
+        <v>574</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868121</t>
+          <t xml:space="preserve">311871425</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-13</t>
+          <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112535</t>
+          <t xml:space="preserve">2116069</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>359</v>
+        <v>519</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868259</t>
+          <t xml:space="preserve">311872911</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831831</t>
+          <t xml:space="preserve">2163217</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>10887</v>
+        <v>425</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868487</t>
+          <t xml:space="preserve">311872910</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-17</t>
+          <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114042</t>
+          <t xml:space="preserve">100086841</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>1096</v>
+        <v>1053</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869557</t>
+          <t xml:space="preserve">311873417</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-21</t>
+          <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114432</t>
+          <t xml:space="preserve">2113825</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,16 +3990,16 @@
         </is>
       </c>
       <c r="F80">
-        <v>574</v>
+        <v>624</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871425</t>
+          <t xml:space="preserve">311873419</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-03</t>
+          <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263211</t>
+          <t xml:space="preserve">1302613</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885140</t>
+          <t xml:space="preserve">311873661</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-03</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163193</t>
+          <t xml:space="preserve">2113868</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>7264</v>
+        <v>369</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871981</t>
+          <t xml:space="preserve">311873659</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163193</t>
+          <t xml:space="preserve">2114911</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>343</v>
+        <v>6301</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871978</t>
+          <t xml:space="preserve">311877723</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163193</t>
+          <t xml:space="preserve">8263211</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F84">
-        <v>1262</v>
+        <v>718</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871983</t>
+          <t xml:space="preserve">311874407</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163193</t>
+          <t xml:space="preserve">8263211</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F85">
-        <v>862</v>
+        <v>395</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871980</t>
+          <t xml:space="preserve">311874407</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116069</t>
+          <t xml:space="preserve">100040742</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>519</v>
+        <v>1658</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872911</t>
+          <t xml:space="preserve">311883945</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-11</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163217</t>
+          <t xml:space="preserve">2163193</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>425</v>
+        <v>7264</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872910</t>
+          <t xml:space="preserve">311879340</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-11</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100086841</t>
+          <t xml:space="preserve">2163193</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F88">
-        <v>1053</v>
+        <v>343</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873417</t>
+          <t xml:space="preserve">311879340</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-14</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113825</t>
+          <t xml:space="preserve">2163193</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F89">
-        <v>624</v>
+        <v>1262</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873419</t>
+          <t xml:space="preserve">311879340</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-14</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302613</t>
+          <t xml:space="preserve">2163193</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>309</v>
+        <v>862</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873661</t>
+          <t xml:space="preserve">311879340</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113868</t>
+          <t xml:space="preserve">8831839</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F91">
-        <v>369</v>
+        <v>1713</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873659</t>
+          <t xml:space="preserve">311879262</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114911</t>
+          <t xml:space="preserve">2115105</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,16 +4590,16 @@
         </is>
       </c>
       <c r="F92">
-        <v>6301</v>
+        <v>9729</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311877723</t>
+          <t xml:space="preserve">311879764</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040742</t>
+          <t xml:space="preserve">2115105</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F93">
-        <v>1658</v>
+        <v>325</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883945</t>
+          <t xml:space="preserve">311882780</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115105</t>
+          <t xml:space="preserve">2115631</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>9729</v>
+        <v>540</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879764</t>
+          <t xml:space="preserve">311883457</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-02</t>
+          <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,25 +4731,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115105</t>
+          <t xml:space="preserve">2115631</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>325</v>
+        <v>540</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882780</t>
+          <t xml:space="preserve">311883457</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-02</t>
+          <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115631</t>
+          <t xml:space="preserve">2116054</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,11 +4790,11 @@
         </is>
       </c>
       <c r="F96">
-        <v>540</v>
+        <v>332</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883457</t>
+          <t xml:space="preserve">311883455</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115631</t>
+          <t xml:space="preserve">2163922</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,11 +4840,11 @@
         </is>
       </c>
       <c r="F97">
-        <v>540</v>
+        <v>309</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883457</t>
+          <t xml:space="preserve">311894044</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116054</t>
+          <t xml:space="preserve">2112535</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F98">
-        <v>332</v>
+        <v>752</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883455</t>
+          <t xml:space="preserve">311886403</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-23</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163922</t>
+          <t xml:space="preserve">2114006</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>309</v>
+        <v>610</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894044</t>
+          <t xml:space="preserve">311886400</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-23</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,20 +4981,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112535</t>
+          <t xml:space="preserve">2114006</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F100">
-        <v>752</v>
+        <v>254</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886403</t>
+          <t xml:space="preserve">311886399</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114006</t>
+          <t xml:space="preserve">2115482</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,11 +5040,11 @@
         </is>
       </c>
       <c r="F101">
-        <v>610</v>
+        <v>504</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886400</t>
+          <t xml:space="preserve">311886397</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114006</t>
+          <t xml:space="preserve">2163599</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>254</v>
+        <v>1385</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886399</t>
+          <t xml:space="preserve">311886396</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115482</t>
+          <t xml:space="preserve">8831848</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="F103">
-        <v>504</v>
+        <v>7706</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886397</t>
+          <t xml:space="preserve">311907854</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163599</t>
+          <t xml:space="preserve">8831848</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F104">
-        <v>1385</v>
+        <v>528</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886396</t>
+          <t xml:space="preserve">311907854</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">226474</t>
+          <t xml:space="preserve">8831848</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F105">
-        <v>284</v>
+        <v>681</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895522</t>
+          <t xml:space="preserve">311907854</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-21</t>
+          <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">

--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:L105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Stadion 22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100959448</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>2855</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Stadion 10</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113866</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>8430</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kærdammen 1B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">226474</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>284</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>524</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>704</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>704</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 4</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>704</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>524</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Guldborgvej 6</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">226530</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>2564</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Strand Centrum 11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">226935, 226960, 226936, 226937, 226938, 226939, 226940, 226941, 226942, 226943, 226944, 226945, 226947, 226948, 226949, 226950, 226951, 226952, 226953, 226954, 226955, 226956, 226958, 226959, 226961, 226963, 226964, 226965, 226966, 226967, 226968, 226946, 226957</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>4989</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Møllevej 25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">226998, 226999</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>6627</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Glentemosen 1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">227000, 227001</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>3449</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Glentemosen 3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">7489614</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>372</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nykær 42C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115661</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>342</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311299608</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygårds Plads 20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115669</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>732</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311317842</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tybjergparken 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163558</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>13498</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311350678</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tybjergparken 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163558</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>418</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311350679</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Riggervej 20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163591</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>1747</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311469956</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndbyøstervej 91</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831859</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>698</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311480758</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-04</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lagesminde Allé 66</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163597</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>899</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311726167</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lagesminde Allé 68</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163597</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>1830</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311726435</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-12-02</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fuglemosen 18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831842</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>621</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311832869</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fuglemosen 20</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831842</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>1008</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311832870</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 35</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114187</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>409</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311840076</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 40</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115106</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>371</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311840069</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311840080</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 38B</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115106</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>389</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311840069</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lundedammen 4A</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115158</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>330</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311840074</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Glentemosen 5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">7489614</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>2478</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311840061</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hesselager 7</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113481</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>2184</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311840942</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lysedammen 42</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114982</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>445</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311841018</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 36A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115125</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>3395</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311840944</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 140</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">7332315</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>573</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311841026</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Glentemosen 15</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">7489614</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>758</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311841028</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tranehaven 25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114362</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>1238</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311843211</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nykær 42A</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115661</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>822</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311843204</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndbytoften 15A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2116268</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>771</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">311843205</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyringparken 9</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2162900</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>498</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">311843217</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyringparken 7</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2162900</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>444</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311843217</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Glentemosen 13</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">7489614</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>718</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311843214</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndbyøstervej 93A</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831859</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>682</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311843203</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Allé 85</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831895</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>566</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311846822</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-07-31</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Stadion 8</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">100035364</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>2396</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311847170</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-08-04</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygårds Plads 31</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831861</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>2783</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311852544</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 46</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115105</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>931</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311855424</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tybjergparken 12</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163558</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>675</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311855487</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Strand Centrum 60</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">100041701</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>3088</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311857077</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredager 160</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302611</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>13180</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311857073</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredager 160</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302611</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>1707</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311857072</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Lindelund 10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302611</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>616</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311857071</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bredager 162</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302611</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>1133</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311857078</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311857079</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanholm Alle 1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">8209831</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>673</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311857070</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyringparken 1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831909</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>11175</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311857074</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyringparken 3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831909</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>545</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311857075</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyringparken 5</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831909</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>2856</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311857076</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tranestien 1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114359</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>254</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311858017</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Stadion 26</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">10081434</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>4875</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311860092</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tornehøj 5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113993</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>713</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311860093</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygårds Plads 30</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115649</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>6380</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311860572</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nygårds Plads 32</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115649</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>4013</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311860572</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sognevej 35</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302613</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>588</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311863004</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 82</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2112485</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>1243</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311863027</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tornehøj 3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113993</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>10309</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311867275</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ulsøparken 71</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2162639</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>534</v>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311863019</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311863033</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanholm Alle 2</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">8209831</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>1006</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311863018</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bygaden 109</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831824</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>257</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311862953</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kettehøjvej 3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163948</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>543</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311864426</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-10-27</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Elementfabrikken 7</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114474</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>2016</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311867157</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-09</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandesplanaden 99</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2162668</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>639</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311867872</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Havnevej 30</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2164045</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>680</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311867867</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Havnevej 20</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2650</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2164045</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>689</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311867867</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ulsøparken 122</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">100095721</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>1770</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311868121</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nybovej 46</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2112535</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>359</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311868258</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Allé 160</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831831</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>10887</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">311868487</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Park Allé 160</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114042</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>1096</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311869557</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ved Kirkebjerg 24</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114432</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>574</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311871425</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Møllevej 10</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2116069</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>519</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311872911</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 296</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163217</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>425</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311872910</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Nord Vej 107</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">100086841</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>1053</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311873417</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Østervang 11</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113825</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>624</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311873419</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sognevej 33</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">1302613</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>309</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311873661</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndbyvester Stræde 3A</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2113868</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>369</v>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311873659</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311873660</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nykær 44</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114911</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>6301</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311877723</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Møllevej 1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">8263211</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>718</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311874407</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndby Møllevej 37</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">8263211</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>395</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311874407</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brøndbyøstervej 156B</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">100040742</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>1658</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311883945</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 300</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163193</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>7264</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311879340</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 300</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163193</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>343</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311879340</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 300</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163193</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>1262</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311879340</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandskolevej 300</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163193</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>862</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311879340</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tranehaven 33</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831839</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>1713</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311879262</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 42</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115105</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>9729</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311879764</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Horsedammen 42C</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115105</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>325</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311882780</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvestien 57</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115631</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>540</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311883457</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvestien 58</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115631</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>540</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311883457</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestre Gade 32</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2116054</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>332</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311883455</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tjørnevangen 9</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163922</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>309</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311894044</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nybovej 22</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2112535</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>752</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311886403</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gildhøj 190</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114006</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>610</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311886400</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gildhøj 188</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2114006</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>254</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311886399</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Turpinsvej 2</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2115482</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>504</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311886397</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lagesminde Allé 60</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2660</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2163599</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>1385</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311886396</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krogagervej 34</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831848</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>7706</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">311907854</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krogagervej 32A</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831848</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>528</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311907854</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,39 +6271,49 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Krogagervej 34</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2605</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">8831848</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>681</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311907854</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J105"/>
+  <autoFilter ref="A1:L105"/>
 </worksheet>
 </file>
--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Stadion 22</t>
+          <t xml:space="preserve">Brøndby Stadion 10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100959448</t>
+          <t xml:space="preserve">2113866</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H2">
-        <v>2855</v>
+        <v>8430</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Stadion 10</t>
+          <t xml:space="preserve">Brøndby Stadion 22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113866</t>
+          <t xml:space="preserve">100959448</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H3">
-        <v>8430</v>
+        <v>2855</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærdammen 1B</t>
+          <t xml:space="preserve">Glentemosen 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">226474</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H4">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 10</t>
+          <t xml:space="preserve">Brøndby Strand Centrum 11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,30 +281,30 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">226935, 226960, 226936, 226937, 226938, 226939, 226940, 226941, 226942, 226943, 226944, 226945, 226947, 226948, 226949, 226950, 226951, 226952, 226953, 226954, 226955, 226956, 226958, 226959, 226961, 226963, 226964, 226965, 226966, 226967, 226968, 226946, 226957</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H5">
-        <v>524</v>
+        <v>4989</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310011650</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-11-02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -331,45 +331,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 14</t>
+          <t xml:space="preserve">Nykær 42C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2115661</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H6">
-        <v>704</v>
+        <v>342</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311299608</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -391,45 +391,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 2</t>
+          <t xml:space="preserve">Nygårds Plads 20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2115669</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311317842</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 4</t>
+          <t xml:space="preserve">Tybjergparken 2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,35 +461,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H8">
-        <v>704</v>
+        <v>13498</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311350678</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 8</t>
+          <t xml:space="preserve">Tybjergparken 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,35 +521,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">226529, 226530</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H9">
-        <v>524</v>
+        <v>418</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311350679</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -571,45 +571,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldborgvej 6</t>
+          <t xml:space="preserve">Brøndby Møllevej 25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">226530</t>
+          <t xml:space="preserve">226998, 226999</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>2564</v>
+        <v>6627</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311366317</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-03-22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Strand Centrum 11</t>
+          <t xml:space="preserve">Guldborgvej 10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,35 +641,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">226935, 226960, 226936, 226937, 226938, 226939, 226940, 226941, 226942, 226943, 226944, 226945, 226947, 226948, 226949, 226950, 226951, 226952, 226953, 226954, 226955, 226956, 226958, 226959, 226961, 226963, 226964, 226965, 226966, 226967, 226968, 226946, 226957</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H11">
-        <v>4989</v>
+        <v>524</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311366950</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -691,45 +691,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Møllevej 25</t>
+          <t xml:space="preserve">Guldborgvej 14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">226998, 226999</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H12">
-        <v>6627</v>
+        <v>704</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311366950</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -751,45 +751,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentemosen 1</t>
+          <t xml:space="preserve">Guldborgvej 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">227000, 227001</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>3449</v>
+        <v>704</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311366950</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -811,45 +811,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentemosen 3</t>
+          <t xml:space="preserve">Guldborgvej 4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H14">
-        <v>372</v>
+        <v>704</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311366950</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -871,35 +871,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykær 42C</t>
+          <t xml:space="preserve">Guldborgvej 6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115661</t>
+          <t xml:space="preserve">226530</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H15">
-        <v>342</v>
+        <v>2564</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299608</t>
+          <t xml:space="preserve">311366938</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-10</t>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -931,35 +931,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårds Plads 20</t>
+          <t xml:space="preserve">Guldborgvej 8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115669</t>
+          <t xml:space="preserve">226529, 226530</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H16">
-        <v>732</v>
+        <v>524</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317842</t>
+          <t xml:space="preserve">311366950</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-01</t>
+          <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tybjergparken 2</t>
+          <t xml:space="preserve">Riggervej 20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,25 +1001,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">2163591</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H17">
-        <v>13498</v>
+        <v>1747</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350678</t>
+          <t xml:space="preserve">311469956</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-09</t>
+          <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1051,35 +1051,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tybjergparken 2</t>
+          <t xml:space="preserve">Brøndbyøstervej 91</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">8831859</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H18">
-        <v>418</v>
+        <v>698</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311350679</t>
+          <t xml:space="preserve">311480758</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-09</t>
+          <t xml:space="preserve">2030-12-04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riggervej 20</t>
+          <t xml:space="preserve">Lagesminde Allé 66</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,25 +1121,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163591</t>
+          <t xml:space="preserve">2163597</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>1747</v>
+        <v>899</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469956</t>
+          <t xml:space="preserve">311726167</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-23</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,17 +1171,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndbyøstervej 91</t>
+          <t xml:space="preserve">Lagesminde Allé 68</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831859</t>
+          <t xml:space="preserve">2163597</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="H20">
-        <v>698</v>
+        <v>1830</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480758</t>
+          <t xml:space="preserve">311726435</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-04</t>
+          <t xml:space="preserve">2033-12-02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1231,17 +1231,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lagesminde Allé 66</t>
+          <t xml:space="preserve">Fuglemosen 18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163597</t>
+          <t xml:space="preserve">8831842</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1250,16 +1250,16 @@
         </is>
       </c>
       <c r="H21">
-        <v>899</v>
+        <v>621</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726167</t>
+          <t xml:space="preserve">311832869</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lagesminde Allé 68</t>
+          <t xml:space="preserve">Fuglemosen 20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163597</t>
+          <t xml:space="preserve">8831842</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="H22">
-        <v>1830</v>
+        <v>1008</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726435</t>
+          <t xml:space="preserve">311832870</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-02</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglemosen 18</t>
+          <t xml:space="preserve">Bygaden 35</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831842</t>
+          <t xml:space="preserve">2114187</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="H23">
-        <v>621</v>
+        <v>409</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832869</t>
+          <t xml:space="preserve">311840076</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglemosen 20</t>
+          <t xml:space="preserve">Glentemosen 1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,25 +1421,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831842</t>
+          <t xml:space="preserve">227000, 227001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>1008</v>
+        <v>3449</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832870</t>
+          <t xml:space="preserve">311840059</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 35</t>
+          <t xml:space="preserve">Glentemosen 5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,20 +1481,20 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114187</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H25">
-        <v>409</v>
+        <v>2478</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840076</t>
+          <t xml:space="preserve">311840061</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 40</t>
+          <t xml:space="preserve">Horsedammen 38B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1546,15 +1546,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H26">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840080</t>
+          <t xml:space="preserve">311840071</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 38B</t>
+          <t xml:space="preserve">Horsedammen 40</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1606,15 +1606,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840069</t>
+          <t xml:space="preserve">311840080</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentemosen 5</t>
+          <t xml:space="preserve">Glentemosen 15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1726,20 +1726,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H29">
-        <v>2478</v>
+        <v>758</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840061</t>
+          <t xml:space="preserve">311841028</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-23</t>
+          <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysedammen 42</t>
+          <t xml:space="preserve">Horsedammen 36A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114982</t>
+          <t xml:space="preserve">2115125</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,11 +1850,11 @@
         </is>
       </c>
       <c r="H31">
-        <v>445</v>
+        <v>3395</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841018</t>
+          <t xml:space="preserve">311840944</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 36A</t>
+          <t xml:space="preserve">Lysedammen 42</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115125</t>
+          <t xml:space="preserve">2114982</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="H32">
-        <v>3395</v>
+        <v>445</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840944</t>
+          <t xml:space="preserve">311841018</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentemosen 15</t>
+          <t xml:space="preserve">Brøndbytoften 15A</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,25 +2021,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">2116268</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841028</t>
+          <t xml:space="preserve">311843205</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-26</t>
+          <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranehaven 25</t>
+          <t xml:space="preserve">Brøndbyøstervej 93A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114362</t>
+          <t xml:space="preserve">8831859</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="H35">
-        <v>1238</v>
+        <v>682</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843211</t>
+          <t xml:space="preserve">311843203</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2131,30 +2131,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykær 42A</t>
+          <t xml:space="preserve">Dyringparken 7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115661</t>
+          <t xml:space="preserve">2162900</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H36">
-        <v>822</v>
+        <v>444</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843204</t>
+          <t xml:space="preserve">311843217</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndbytoften 15A</t>
+          <t xml:space="preserve">Dyringparken 9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116268</t>
+          <t xml:space="preserve">2162900</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2210,11 +2210,11 @@
         </is>
       </c>
       <c r="H37">
-        <v>771</v>
+        <v>498</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843205</t>
+          <t xml:space="preserve">311843217</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyringparken 9</t>
+          <t xml:space="preserve">Glentemosen 13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162900</t>
+          <t xml:space="preserve">7489614</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,11 +2270,11 @@
         </is>
       </c>
       <c r="H38">
-        <v>498</v>
+        <v>718</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843217</t>
+          <t xml:space="preserve">311843214</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,30 +2311,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyringparken 7</t>
+          <t xml:space="preserve">Nykær 42A</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162900</t>
+          <t xml:space="preserve">2115661</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>444</v>
+        <v>822</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843217</t>
+          <t xml:space="preserve">311843204</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glentemosen 13</t>
+          <t xml:space="preserve">Tranehaven 25</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7489614</t>
+          <t xml:space="preserve">2114362</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,11 +2390,11 @@
         </is>
       </c>
       <c r="H40">
-        <v>718</v>
+        <v>1238</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843214</t>
+          <t xml:space="preserve">311843211</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndbyøstervej 93A</t>
+          <t xml:space="preserve">Park Allé 85</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831859</t>
+          <t xml:space="preserve">8831895</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,16 +2450,16 @@
         </is>
       </c>
       <c r="H41">
-        <v>682</v>
+        <v>566</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311843203</t>
+          <t xml:space="preserve">311846822</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-07</t>
+          <t xml:space="preserve">2035-07-31</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Allé 85</t>
+          <t xml:space="preserve">Brøndby Stadion 8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831895</t>
+          <t xml:space="preserve">100035364</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,16 +2510,16 @@
         </is>
       </c>
       <c r="H42">
-        <v>566</v>
+        <v>2396</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311846822</t>
+          <t xml:space="preserve">311847170</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-31</t>
+          <t xml:space="preserve">2035-08-04</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Stadion 8</t>
+          <t xml:space="preserve">Nygårds Plads 31</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035364</t>
+          <t xml:space="preserve">8831861</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2570,16 +2570,16 @@
         </is>
       </c>
       <c r="H43">
-        <v>2396</v>
+        <v>2783</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847170</t>
+          <t xml:space="preserve">311852544</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-04</t>
+          <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårds Plads 31</t>
+          <t xml:space="preserve">Horsedammen 46</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831861</t>
+          <t xml:space="preserve">2115105</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H44">
-        <v>2783</v>
+        <v>931</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852544</t>
+          <t xml:space="preserve">311855424</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-29</t>
+          <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,30 +2671,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 46</t>
+          <t xml:space="preserve">Tybjergparken 12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115105</t>
+          <t xml:space="preserve">2163558</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H45">
-        <v>931</v>
+        <v>675</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855424</t>
+          <t xml:space="preserve">311855487</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tybjergparken 12</t>
+          <t xml:space="preserve">Bredager 160</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163558</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>675</v>
+        <v>13180</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311855487</t>
+          <t xml:space="preserve">311857073</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-12</t>
+          <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,30 +2791,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Strand Centrum 60</t>
+          <t xml:space="preserve">Bredager 160</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100041701</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>3088</v>
+        <v>1707</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857077</t>
+          <t xml:space="preserve">311857072</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredager 160</t>
+          <t xml:space="preserve">Bredager 162</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2866,15 +2866,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H48">
-        <v>13180</v>
+        <v>1133</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857073</t>
+          <t xml:space="preserve">311857078</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,30 +2911,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredager 160</t>
+          <t xml:space="preserve">Brøndby Strand Centrum 60</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">100041701</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1707</v>
+        <v>3088</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857072</t>
+          <t xml:space="preserve">311857077</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2971,30 +2971,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Lindelund 10</t>
+          <t xml:space="preserve">Dyringparken 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>616</v>
+        <v>11175</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857071</t>
+          <t xml:space="preserve">311857074</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3031,30 +3031,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredager 162</t>
+          <t xml:space="preserve">Dyringparken 3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302611</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H51">
-        <v>1133</v>
+        <v>545</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857079</t>
+          <t xml:space="preserve">311857075</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholm Alle 1</t>
+          <t xml:space="preserve">Dyringparken 5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8209831</t>
+          <t xml:space="preserve">8831909</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3110,11 +3110,11 @@
         </is>
       </c>
       <c r="H52">
-        <v>673</v>
+        <v>2856</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857070</t>
+          <t xml:space="preserve">311857076</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyringparken 1</t>
+          <t xml:space="preserve">Svanholm Alle 1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,20 +3161,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">8209831</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H53">
-        <v>11175</v>
+        <v>673</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857074</t>
+          <t xml:space="preserve">311857070</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3211,30 +3211,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyringparken 3</t>
+          <t xml:space="preserve">Ved Lindelund 10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">1302611</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H54">
-        <v>545</v>
+        <v>616</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857075</t>
+          <t xml:space="preserve">311857071</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyringparken 5</t>
+          <t xml:space="preserve">Tranestien 1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831909</t>
+          <t xml:space="preserve">2114359</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>2856</v>
+        <v>254</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857076</t>
+          <t xml:space="preserve">311858017</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-20</t>
+          <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranestien 1</t>
+          <t xml:space="preserve">Brøndby Stadion 26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114359</t>
+          <t xml:space="preserve">10081434</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>254</v>
+        <v>4875</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858017</t>
+          <t xml:space="preserve">311860092</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-25</t>
+          <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Stadion 26</t>
+          <t xml:space="preserve">Tornehøj 5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,20 +3401,20 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">10081434</t>
+          <t xml:space="preserve">2113993</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H57">
-        <v>4875</v>
+        <v>713</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860092</t>
+          <t xml:space="preserve">311860093</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornehøj 5</t>
+          <t xml:space="preserve">Nygårds Plads 30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113993</t>
+          <t xml:space="preserve">2115649</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>713</v>
+        <v>6380</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860093</t>
+          <t xml:space="preserve">311860572</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-06</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårds Plads 30</t>
+          <t xml:space="preserve">Nygårds Plads 32</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3526,11 +3526,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H59">
-        <v>6380</v>
+        <v>4013</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygårds Plads 32</t>
+          <t xml:space="preserve">Bygaden 109</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115649</t>
+          <t xml:space="preserve">8831824</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>4013</v>
+        <v>257</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860572</t>
+          <t xml:space="preserve">311862953</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 35</t>
+          <t xml:space="preserve">Bygaden 82</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,20 +3641,20 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302613</t>
+          <t xml:space="preserve">2112485</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>588</v>
+        <v>1243</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863004</t>
+          <t xml:space="preserve">311863027</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 82</t>
+          <t xml:space="preserve">Sognevej 35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,20 +3701,20 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112485</t>
+          <t xml:space="preserve">1302613</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H62">
-        <v>1243</v>
+        <v>588</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863027</t>
+          <t xml:space="preserve">311863006</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornehøj 3</t>
+          <t xml:space="preserve">Svanholm Alle 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113993</t>
+          <t xml:space="preserve">8209831</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3770,11 +3770,11 @@
         </is>
       </c>
       <c r="H63">
-        <v>10309</v>
+        <v>1006</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867275</t>
+          <t xml:space="preserve">311863018</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3811,30 +3811,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulsøparken 71</t>
+          <t xml:space="preserve">Tornehøj 3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162639</t>
+          <t xml:space="preserve">2113993</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H64">
-        <v>534</v>
+        <v>10309</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863033</t>
+          <t xml:space="preserve">311867275</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholm Alle 2</t>
+          <t xml:space="preserve">Ulsøparken 71</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,20 +3881,20 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8209831</t>
+          <t xml:space="preserve">2162639</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>1006</v>
+        <v>534</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863018</t>
+          <t xml:space="preserve">311863022</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 109</t>
+          <t xml:space="preserve">Kettehøjvej 3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831824</t>
+          <t xml:space="preserve">2163948</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3950,16 +3950,16 @@
         </is>
       </c>
       <c r="H66">
-        <v>257</v>
+        <v>543</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862953</t>
+          <t xml:space="preserve">311864426</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-20</t>
+          <t xml:space="preserve">2035-10-27</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettehøjvej 3</t>
+          <t xml:space="preserve">Elementfabrikken 7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163948</t>
+          <t xml:space="preserve">2114474</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>543</v>
+        <v>2016</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311864426</t>
+          <t xml:space="preserve">311867157</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-27</t>
+          <t xml:space="preserve">2035-11-09</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elementfabrikken 7</t>
+          <t xml:space="preserve">Brøndby Havnevej 20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114474</t>
+          <t xml:space="preserve">2164045</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H68">
-        <v>2016</v>
+        <v>689</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867157</t>
+          <t xml:space="preserve">311867867</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-09</t>
+          <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,30 +4111,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandesplanaden 99</t>
+          <t xml:space="preserve">Brøndby Havnevej 30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2650</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162668</t>
+          <t xml:space="preserve">2164045</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H69">
-        <v>639</v>
+        <v>680</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867872</t>
+          <t xml:space="preserve">311867867</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4171,30 +4171,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Havnevej 30</t>
+          <t xml:space="preserve">Strandesplanaden 99</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164045</t>
+          <t xml:space="preserve">2162668</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H70">
-        <v>680</v>
+        <v>639</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867867</t>
+          <t xml:space="preserve">311867872</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Havnevej 20</t>
+          <t xml:space="preserve">Ulsøparken 122</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2650</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164045</t>
+          <t xml:space="preserve">100095721</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>689</v>
+        <v>1770</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311867867</t>
+          <t xml:space="preserve">311868121</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-12</t>
+          <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulsøparken 122</t>
+          <t xml:space="preserve">Nybovej 46</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100095721</t>
+          <t xml:space="preserve">2112535</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H72">
-        <v>1770</v>
+        <v>359</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868121</t>
+          <t xml:space="preserve">311868259</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-13</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybovej 46</t>
+          <t xml:space="preserve">Park Allé 160</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4361,25 +4361,25 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112535</t>
+          <t xml:space="preserve">8831831</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>359</v>
+        <v>10887</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868258</t>
+          <t xml:space="preserve">311868487</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831831</t>
+          <t xml:space="preserve">2114042</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>10887</v>
+        <v>1096</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868487</t>
+          <t xml:space="preserve">311869557</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-17</t>
+          <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Park Allé 160</t>
+          <t xml:space="preserve">Ved Kirkebjerg 24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114042</t>
+          <t xml:space="preserve">2114432</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>1096</v>
+        <v>574</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869557</t>
+          <t xml:space="preserve">311871425</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-21</t>
+          <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Kirkebjerg 24</t>
+          <t xml:space="preserve">Brøndby Møllevej 10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4541,25 +4541,25 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114432</t>
+          <t xml:space="preserve">2116069</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H76">
-        <v>574</v>
+        <v>519</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871425</t>
+          <t xml:space="preserve">311872911</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-03</t>
+          <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,30 +4591,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Møllevej 10</t>
+          <t xml:space="preserve">Strandskolevej 296</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116069</t>
+          <t xml:space="preserve">2163217</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>519</v>
+        <v>425</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872911</t>
+          <t xml:space="preserve">311872910</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandskolevej 296</t>
+          <t xml:space="preserve">Brøndby Nord Vej 107</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163217</t>
+          <t xml:space="preserve">100086841</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>425</v>
+        <v>1053</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872910</t>
+          <t xml:space="preserve">311873417</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-11</t>
+          <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Nord Vej 107</t>
+          <t xml:space="preserve">Østervang 11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">100086841</t>
+          <t xml:space="preserve">2113825</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,11 +4730,11 @@
         </is>
       </c>
       <c r="H79">
-        <v>1053</v>
+        <v>624</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873417</t>
+          <t xml:space="preserve">311873419</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 11</t>
+          <t xml:space="preserve">Brøndbyvester Stræde 3A</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113825</t>
+          <t xml:space="preserve">2113868</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="H80">
-        <v>624</v>
+        <v>369</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873419</t>
+          <t xml:space="preserve">311873659</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-14</t>
+          <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndbyvester Stræde 3A</t>
+          <t xml:space="preserve">Nykær 44</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2113868</t>
+          <t xml:space="preserve">2114911</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>369</v>
+        <v>6301</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873660</t>
+          <t xml:space="preserve">311877723</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-16</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nykær 44</t>
+          <t xml:space="preserve">Brøndby Møllevej 1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,25 +4961,25 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114911</t>
+          <t xml:space="preserve">8263211</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>6301</v>
+        <v>718</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311877723</t>
+          <t xml:space="preserve">311874407</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Møllevej 1</t>
+          <t xml:space="preserve">Brøndby Møllevej 37</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5026,11 +5026,11 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H84">
-        <v>718</v>
+        <v>395</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndby Møllevej 37</t>
+          <t xml:space="preserve">Brøndbyøstervej 156B</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263211</t>
+          <t xml:space="preserve">100040742</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>395</v>
+        <v>1658</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874407</t>
+          <t xml:space="preserve">311883945</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-19</t>
+          <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brøndbyøstervej 156B</t>
+          <t xml:space="preserve">Strandskolevej 300</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040742</t>
+          <t xml:space="preserve">2163193</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,11 +5150,11 @@
         </is>
       </c>
       <c r="H86">
-        <v>1658</v>
+        <v>7264</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883945</t>
+          <t xml:space="preserve">311879340</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5206,11 +5206,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H87">
-        <v>7264</v>
+        <v>343</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5266,11 +5266,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H88">
-        <v>343</v>
+        <v>1262</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5326,11 +5326,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H89">
-        <v>1262</v>
+        <v>862</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,30 +5371,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandskolevej 300</t>
+          <t xml:space="preserve">Tranehaven 33</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163193</t>
+          <t xml:space="preserve">8831839</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H90">
-        <v>862</v>
+        <v>1713</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879340</t>
+          <t xml:space="preserve">311879262</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranehaven 33</t>
+          <t xml:space="preserve">Horsedammen 42</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831839</t>
+          <t xml:space="preserve">2115105</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>1713</v>
+        <v>9729</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879262</t>
+          <t xml:space="preserve">311879764</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-29</t>
+          <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 42</t>
+          <t xml:space="preserve">Horsedammen 42C</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5506,15 +5506,15 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H92">
-        <v>9729</v>
+        <v>325</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879764</t>
+          <t xml:space="preserve">311882780</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5551,35 +5551,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsedammen 42C</t>
+          <t xml:space="preserve">Tjørnevangen 9</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115105</t>
+          <t xml:space="preserve">2163922</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H93">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882780</t>
+          <t xml:space="preserve">311894044</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-02</t>
+          <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjørnevangen 9</t>
+          <t xml:space="preserve">Gildhøj 188</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163922</t>
+          <t xml:space="preserve">2114006</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311894044</t>
+          <t xml:space="preserve">311886399</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-23</t>
+          <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybovej 22</t>
+          <t xml:space="preserve">Gildhøj 190</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,20 +5861,20 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112535</t>
+          <t xml:space="preserve">2114006</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>752</v>
+        <v>610</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886403</t>
+          <t xml:space="preserve">311886400</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gildhøj 190</t>
+          <t xml:space="preserve">Lagesminde Allé 60</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">2660</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114006</t>
+          <t xml:space="preserve">2163599</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,11 +5930,11 @@
         </is>
       </c>
       <c r="H99">
-        <v>610</v>
+        <v>1385</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886400</t>
+          <t xml:space="preserve">311886396</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gildhøj 188</t>
+          <t xml:space="preserve">Nybovej 22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114006</t>
+          <t xml:space="preserve">2112535</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H100">
-        <v>254</v>
+        <v>752</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886399</t>
+          <t xml:space="preserve">311886403</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6091,35 +6091,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lagesminde Allé 60</t>
+          <t xml:space="preserve">Kærdammen 1B</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2660</t>
+          <t xml:space="preserve">2605</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163599</t>
+          <t xml:space="preserve">226474</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H102">
-        <v>1385</v>
+        <v>284</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886396</t>
+          <t xml:space="preserve">311895522</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-10</t>
+          <t xml:space="preserve">2036-04-21</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogagervej 34</t>
+          <t xml:space="preserve">Krogagervej 32A</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6166,11 +6166,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H103">
-        <v>7706</v>
+        <v>528</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogagervej 32A</t>
+          <t xml:space="preserve">Krogagervej 34</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6226,11 +6226,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H104">
-        <v>528</v>
+        <v>7706</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>

--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840071</t>
+          <t xml:space="preserve">311840069</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840080</t>
+          <t xml:space="preserve">311840069</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857073</t>
+          <t xml:space="preserve">311857079</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857078</t>
+          <t xml:space="preserve">311857079</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863006</t>
+          <t xml:space="preserve">311863004</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868259</t>
+          <t xml:space="preserve">311868258</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">

--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:M105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -299,15 +319,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-02</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -359,15 +384,20 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -419,15 +449,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl ApS</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-06-01</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -479,15 +514,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -539,15 +579,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-09</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -599,15 +644,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-22</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">RIOS A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-26</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-23</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-04</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-02</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-23</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-26</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-07</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-31</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-04</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-29</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-12</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2874,20 +3109,25 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857079</t>
+          <t xml:space="preserve">311857078</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-20</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-25</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-06</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3714,20 +4019,25 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863004</t>
+          <t xml:space="preserve">311863006</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-20</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-10-27</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-09</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-12</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4314,20 +4669,25 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868258</t>
+          <t xml:space="preserve">311868259</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-21</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-03</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-14</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-16</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-19</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-29</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-10</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Artelia A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-04-21</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,21 +6819,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-12</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L105"/>
+  <autoFilter ref="A1:M105"/>
 </worksheet>
 </file>
--- a/public/exports/65113015.xlsx
+++ b/public/exports/65113015.xlsx
@@ -2979,7 +2979,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311857079</t>
+          <t xml:space="preserve">311857073</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863006</t>
+          <t xml:space="preserve">311863004</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863022</t>
+          <t xml:space="preserve">311863019</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868259</t>
+          <t xml:space="preserve">311868258</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
